--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_30-07-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_30-07-2025.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>£18.75</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -638,25 +638,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -739,25 +739,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -797,17 +797,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>£16.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>£16.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>£16.60</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -840,25 +840,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -941,25 +941,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1042,25 +1042,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1143,25 +1143,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1244,25 +1244,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1345,25 +1345,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1547,25 +1547,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1648,25 +1648,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1826,25 +1826,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£40.0</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1927,25 +1927,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
@@ -2028,25 +2028,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff686bfe415+77285]
-	GetHandleVerifier [0x0x7ff686bfe470+77376]
-	(No symbol) [0x0x7ff6869c9a6a]
-	(No symbol) [0x0x7ff686a20406]
-	(No symbol) [0x0x7ff686a206bc]
-	(No symbol) [0x0x7ff686a73ac7]
-	(No symbol) [0x0x7ff686a4864f]
-	(No symbol) [0x0x7ff686a7087f]
-	(No symbol) [0x0x7ff686a483e3]
-	(No symbol) [0x0x7ff686a11521]
-	(No symbol) [0x0x7ff686a122b3]
-	GetHandleVerifier [0x0x7ff686ee1efd+3107021]
-	GetHandleVerifier [0x0x7ff686edc29d+3083373]
-	GetHandleVerifier [0x0x7ff686efbedd+3213485]
-	GetHandleVerifier [0x0x7ff686c1884e+184862]
-	GetHandleVerifier [0x0x7ff686c2055f+216879]
-	GetHandleVerifier [0x0x7ff686c07084+113236]
-	GetHandleVerifier [0x0x7ff686c07239+113673]
-	GetHandleVerifier [0x0x7ff686bee298+11368]
+	GetHandleVerifier [0x0x7ff6f7d5e415+77285]
+	GetHandleVerifier [0x0x7ff6f7d5e470+77376]
+	(No symbol) [0x0x7ff6f7b29a6a]
+	(No symbol) [0x0x7ff6f7b80406]
+	(No symbol) [0x0x7ff6f7b806bc]
+	(No symbol) [0x0x7ff6f7bd3ac7]
+	(No symbol) [0x0x7ff6f7ba864f]
+	(No symbol) [0x0x7ff6f7bd087f]
+	(No symbol) [0x0x7ff6f7ba83e3]
+	(No symbol) [0x0x7ff6f7b71521]
+	(No symbol) [0x0x7ff6f7b722b3]
+	GetHandleVerifier [0x0x7ff6f8041efd+3107021]
+	GetHandleVerifier [0x0x7ff6f803c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f805bedd+3213485]
+	GetHandleVerifier [0x0x7ff6f7d7884e+184862]
+	GetHandleVerifier [0x0x7ff6f7d8055f+216879]
+	GetHandleVerifier [0x0x7ff6f7d67084+113236]
+	GetHandleVerifier [0x0x7ff6f7d67239+113673]
+	GetHandleVerifier [0x0x7ff6f7d4e298+11368]
 	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
 	RtlUserThreadStart [0x0x7ffc093fc34c+44]
 </t>
